--- a/docs/DD_北海道3町_20261016/PX案件チェックシート_遠別町丸松.xlsx
+++ b/docs/DD_北海道3町_20261016/PX案件チェックシート_遠別町丸松.xlsx
@@ -582,7 +582,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>作成日：2026-10-16</t>
+          <t>作成日：2026-10-19</t>
         </is>
       </c>
     </row>
@@ -1045,9 +1045,9 @@
           <t>6. 液状化危険度</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>液状化しにくい（砂礫質台地）</t>
         </is>
       </c>
       <c r="F8" s="16" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>J-SHIS表層地盤＋各都道府県の液状化マップで確認。</t>
+          <t>J-SHIS表層地盤＋各都道府県の液状化マップで確認。 / 不動産情報ライブラリ（3筆）</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>自治体の都市計画情報(web GIS)で区域区分を確認。 / 国土数値情報 都市地域(2018)に当町の都市計画区域の指定なし</t>
+          <t>自治体の都市計画情報(web GIS)で区域区分を確認。 / 国土数値情報 都市地域(2018)に当町の都市計画区域の指定なし／不動産情報ライブラリでも区域区分・用途地域なし</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>地点はGoogleマップ航空写真（座標）で確認。農地区分はeMAFF農地ナビ（住所/地番検索）、種別(1/2/3種)は農業委員会へ照会。 / 地目は山林（出典：法務省地図XML(G空間 2026)の筆ポリゴン×国土数値情報 土地利用基本計画(2015)／地理院ハザードタイル。1/2.5万〜5万精度のため境界付近は要確認）</t>
+          <t>地点はGoogleマップ航空写真（座標）で確認。農地区分はeMAFF農地ナビ（住所/地番検索）、種別(1/2/3種)は農業委員会へ照会。 / 地目は山林（出典：不動産情報ライブラリ(2026-10-19取得)／法務省地図XML(G空間 2026)の筆ポリゴン×国土数値情報 土地利用基本計画(2015)／地理院ハザードタイル。1/2.5万〜5万精度のため境界付近は要確認）</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
